--- a/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_visits_users.xlsx
+++ b/OMOP Analysis/Results/SecondaryCareAnalysis/Comparison/OP/monthly_bootstrap_combined_data_visits_users.xlsx
@@ -421,34 +421,34 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>239.905</v>
+        <v>1.665</v>
       </c>
       <c r="C2">
-        <v>4.832</v>
+        <v>0</v>
       </c>
       <c r="D2">
-        <v>2.198</v>
+        <v>0.015</v>
       </c>
       <c r="E2">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>235.656</v>
+        <v>1.637</v>
       </c>
       <c r="G2">
-        <v>244.273</v>
+        <v>1.694</v>
       </c>
       <c r="H2">
-        <v>235.629</v>
+        <v>1.637</v>
       </c>
       <c r="I2">
-        <v>243.948</v>
+        <v>1.694</v>
       </c>
       <c r="J2">
-        <v>235.922</v>
+        <v>1.636</v>
       </c>
       <c r="K2">
-        <v>244.241</v>
+        <v>1.694</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
@@ -461,34 +461,34 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>159.44</v>
+        <v>1.187</v>
       </c>
       <c r="C3">
-        <v>2.608</v>
+        <v>0</v>
       </c>
       <c r="D3">
-        <v>1.615</v>
+        <v>0.014</v>
       </c>
       <c r="E3">
-        <v>0.051</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>156.2</v>
+        <v>1.161</v>
       </c>
       <c r="G3">
-        <v>162.53</v>
+        <v>1.214</v>
       </c>
       <c r="H3">
-        <v>156.071</v>
+        <v>1.16</v>
       </c>
       <c r="I3">
-        <v>162.445</v>
+        <v>1.212</v>
       </c>
       <c r="J3">
-        <v>156.359</v>
+        <v>1.162</v>
       </c>
       <c r="K3">
-        <v>162.734</v>
+        <v>1.215</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -501,34 +501,34 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>105.234</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="C4">
-        <v>2.016</v>
+        <v>0</v>
       </c>
       <c r="D4">
-        <v>1.42</v>
+        <v>0.01</v>
       </c>
       <c r="E4">
-        <v>0.045</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>102.367</v>
+        <v>0.788</v>
       </c>
       <c r="G4">
-        <v>107.933</v>
+        <v>0.827</v>
       </c>
       <c r="H4">
-        <v>102.418</v>
+        <v>0.787</v>
       </c>
       <c r="I4">
-        <v>107.952</v>
+        <v>0.827</v>
       </c>
       <c r="J4">
-        <v>102.433</v>
+        <v>0.788</v>
       </c>
       <c r="K4">
-        <v>107.966</v>
+        <v>0.828</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -541,34 +541,34 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>74.93300000000001</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C5">
-        <v>2.466</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1.57</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="E5">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>71.703</v>
+        <v>0.549</v>
       </c>
       <c r="G5">
-        <v>77.85899999999999</v>
+        <v>0.583</v>
       </c>
       <c r="H5">
-        <v>71.495</v>
+        <v>0.55</v>
       </c>
       <c r="I5">
-        <v>77.654</v>
+        <v>0.582</v>
       </c>
       <c r="J5">
-        <v>72.06100000000001</v>
+        <v>0.55</v>
       </c>
       <c r="K5">
-        <v>78.21899999999999</v>
+        <v>0.583</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
@@ -581,34 +581,34 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>57.501</v>
+        <v>0.432</v>
       </c>
       <c r="C6">
-        <v>0.931</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0.965</v>
+        <v>0.007</v>
       </c>
       <c r="E6">
-        <v>0.031</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>55.659</v>
+        <v>0.418</v>
       </c>
       <c r="G6">
-        <v>59.442</v>
+        <v>0.446</v>
       </c>
       <c r="H6">
-        <v>55.659</v>
+        <v>0.418</v>
       </c>
       <c r="I6">
-        <v>59.439</v>
+        <v>0.446</v>
       </c>
       <c r="J6">
-        <v>55.613</v>
+        <v>0.418</v>
       </c>
       <c r="K6">
-        <v>59.393</v>
+        <v>0.446</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
@@ -621,34 +621,34 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>46.776</v>
+        <v>0.346</v>
       </c>
       <c r="C7">
-        <v>0.819</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.905</v>
+        <v>0.006</v>
       </c>
       <c r="E7">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>45.02</v>
+        <v>0.333</v>
       </c>
       <c r="G7">
-        <v>48.568</v>
+        <v>0.359</v>
       </c>
       <c r="H7">
-        <v>45.037</v>
+        <v>0.333</v>
       </c>
       <c r="I7">
-        <v>48.489</v>
+        <v>0.359</v>
       </c>
       <c r="J7">
-        <v>45.08</v>
+        <v>0.334</v>
       </c>
       <c r="K7">
-        <v>48.533</v>
+        <v>0.359</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
@@ -661,34 +661,34 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>40.338</v>
+        <v>0.291</v>
       </c>
       <c r="C8">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="D8">
-        <v>0.843</v>
+        <v>0.006</v>
       </c>
       <c r="E8">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>38.724</v>
+        <v>0.279</v>
       </c>
       <c r="G8">
-        <v>42.028</v>
+        <v>0.302</v>
       </c>
       <c r="H8">
-        <v>38.643</v>
+        <v>0.279</v>
       </c>
       <c r="I8">
-        <v>42.007</v>
+        <v>0.302</v>
       </c>
       <c r="J8">
-        <v>38.707</v>
+        <v>0.279</v>
       </c>
       <c r="K8">
-        <v>42.071</v>
+        <v>0.302</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
@@ -701,34 +701,34 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>34.879</v>
+        <v>0.25</v>
       </c>
       <c r="C9">
-        <v>0.621</v>
+        <v>0</v>
       </c>
       <c r="D9">
-        <v>0.788</v>
+        <v>0.005</v>
       </c>
       <c r="E9">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>33.312</v>
+        <v>0.239</v>
       </c>
       <c r="G9">
-        <v>36.401</v>
+        <v>0.26</v>
       </c>
       <c r="H9">
-        <v>33.244</v>
+        <v>0.239</v>
       </c>
       <c r="I9">
-        <v>36.395</v>
+        <v>0.26</v>
       </c>
       <c r="J9">
-        <v>33.341</v>
+        <v>0.239</v>
       </c>
       <c r="K9">
-        <v>36.491</v>
+        <v>0.26</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -741,34 +741,34 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>31.263</v>
+        <v>0.223</v>
       </c>
       <c r="C10">
-        <v>0.538</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0.734</v>
+        <v>0.005</v>
       </c>
       <c r="E10">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>29.811</v>
+        <v>0.213</v>
       </c>
       <c r="G10">
-        <v>32.687</v>
+        <v>0.232</v>
       </c>
       <c r="H10">
-        <v>29.799</v>
+        <v>0.213</v>
       </c>
       <c r="I10">
-        <v>32.689</v>
+        <v>0.232</v>
       </c>
       <c r="J10">
-        <v>29.822</v>
+        <v>0.214</v>
       </c>
       <c r="K10">
-        <v>32.712</v>
+        <v>0.233</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -781,34 +781,34 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>30.158</v>
+        <v>0.213</v>
       </c>
       <c r="C11">
-        <v>0.492</v>
+        <v>0</v>
       </c>
       <c r="D11">
-        <v>0.701</v>
+        <v>0.005</v>
       </c>
       <c r="E11">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <v>28.76</v>
+        <v>0.204</v>
       </c>
       <c r="G11">
-        <v>31.508</v>
+        <v>0.222</v>
       </c>
       <c r="H11">
-        <v>28.732</v>
+        <v>0.203</v>
       </c>
       <c r="I11">
-        <v>31.471</v>
+        <v>0.222</v>
       </c>
       <c r="J11">
-        <v>28.821</v>
+        <v>0.204</v>
       </c>
       <c r="K11">
-        <v>31.56</v>
+        <v>0.222</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -821,34 +821,34 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>28.092</v>
+        <v>0.198</v>
       </c>
       <c r="C12">
-        <v>0.555</v>
+        <v>0</v>
       </c>
       <c r="D12">
-        <v>0.745</v>
+        <v>0.005</v>
       </c>
       <c r="E12">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <v>26.543</v>
+        <v>0.188</v>
       </c>
       <c r="G12">
-        <v>29.464</v>
+        <v>0.208</v>
       </c>
       <c r="H12">
-        <v>26.44</v>
+        <v>0.188</v>
       </c>
       <c r="I12">
-        <v>29.48</v>
+        <v>0.207</v>
       </c>
       <c r="J12">
-        <v>26.615</v>
+        <v>0.189</v>
       </c>
       <c r="K12">
-        <v>29.655</v>
+        <v>0.208</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
@@ -861,34 +861,34 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>28.921</v>
+        <v>0.202</v>
       </c>
       <c r="C13">
-        <v>0.504</v>
+        <v>0</v>
       </c>
       <c r="D13">
-        <v>0.71</v>
+        <v>0.004</v>
       </c>
       <c r="E13">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>27.487</v>
+        <v>0.194</v>
       </c>
       <c r="G13">
-        <v>30.271</v>
+        <v>0.211</v>
       </c>
       <c r="H13">
-        <v>27.418</v>
+        <v>0.193</v>
       </c>
       <c r="I13">
-        <v>30.272</v>
+        <v>0.211</v>
       </c>
       <c r="J13">
-        <v>27.529</v>
+        <v>0.194</v>
       </c>
       <c r="K13">
-        <v>30.383</v>
+        <v>0.211</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -901,34 +901,34 @@
         <v>13</v>
       </c>
       <c r="B14">
-        <v>24.682</v>
+        <v>0.174</v>
       </c>
       <c r="C14">
-        <v>0.365</v>
+        <v>0</v>
       </c>
       <c r="D14">
-        <v>0.604</v>
+        <v>0.004</v>
       </c>
       <c r="E14">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>23.491</v>
+        <v>0.166</v>
       </c>
       <c r="G14">
-        <v>25.86</v>
+        <v>0.181</v>
       </c>
       <c r="H14">
-        <v>23.517</v>
+        <v>0.165</v>
       </c>
       <c r="I14">
-        <v>25.803</v>
+        <v>0.181</v>
       </c>
       <c r="J14">
-        <v>23.555</v>
+        <v>0.166</v>
       </c>
       <c r="K14">
-        <v>25.84</v>
+        <v>0.182</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
@@ -941,34 +941,34 @@
         <v>14</v>
       </c>
       <c r="B15">
-        <v>24.888</v>
+        <v>0.171</v>
       </c>
       <c r="C15">
-        <v>0.399</v>
+        <v>0</v>
       </c>
       <c r="D15">
-        <v>0.632</v>
+        <v>0.004</v>
       </c>
       <c r="E15">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>23.657</v>
+        <v>0.164</v>
       </c>
       <c r="G15">
-        <v>26.133</v>
+        <v>0.179</v>
       </c>
       <c r="H15">
-        <v>23.668</v>
+        <v>0.164</v>
       </c>
       <c r="I15">
-        <v>26.115</v>
+        <v>0.179</v>
       </c>
       <c r="J15">
-        <v>23.669</v>
+        <v>0.164</v>
       </c>
       <c r="K15">
-        <v>26.115</v>
+        <v>0.179</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
@@ -981,34 +981,34 @@
         <v>15</v>
       </c>
       <c r="B16">
-        <v>23.195</v>
+        <v>0.163</v>
       </c>
       <c r="C16">
-        <v>0.437</v>
+        <v>0</v>
       </c>
       <c r="D16">
-        <v>0.661</v>
+        <v>0.004</v>
       </c>
       <c r="E16">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <v>21.84</v>
+        <v>0.155</v>
       </c>
       <c r="G16">
-        <v>24.43</v>
+        <v>0.171</v>
       </c>
       <c r="H16">
-        <v>21.805</v>
+        <v>0.154</v>
       </c>
       <c r="I16">
-        <v>24.377</v>
+        <v>0.17</v>
       </c>
       <c r="J16">
-        <v>21.953</v>
+        <v>0.155</v>
       </c>
       <c r="K16">
-        <v>24.525</v>
+        <v>0.171</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
@@ -1021,34 +1021,34 @@
         <v>16</v>
       </c>
       <c r="B17">
-        <v>23.018</v>
+        <v>0.162</v>
       </c>
       <c r="C17">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="D17">
-        <v>0.625</v>
+        <v>0.004</v>
       </c>
       <c r="E17">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <v>21.747</v>
+        <v>0.154</v>
       </c>
       <c r="G17">
-        <v>24.198</v>
+        <v>0.171</v>
       </c>
       <c r="H17">
-        <v>21.732</v>
+        <v>0.154</v>
       </c>
       <c r="I17">
-        <v>24.23</v>
+        <v>0.17</v>
       </c>
       <c r="J17">
-        <v>21.761</v>
+        <v>0.154</v>
       </c>
       <c r="K17">
-        <v>24.259</v>
+        <v>0.171</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
@@ -1061,34 +1061,34 @@
         <v>17</v>
       </c>
       <c r="B18">
-        <v>22.642</v>
+        <v>0.158</v>
       </c>
       <c r="C18">
-        <v>0.415</v>
+        <v>0</v>
       </c>
       <c r="D18">
-        <v>0.644</v>
+        <v>0.004</v>
       </c>
       <c r="E18">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <v>21.365</v>
+        <v>0.149</v>
       </c>
       <c r="G18">
-        <v>23.889</v>
+        <v>0.166</v>
       </c>
       <c r="H18">
-        <v>21.309</v>
+        <v>0.149</v>
       </c>
       <c r="I18">
-        <v>23.829</v>
+        <v>0.166</v>
       </c>
       <c r="J18">
-        <v>21.439</v>
+        <v>0.149</v>
       </c>
       <c r="K18">
-        <v>23.959</v>
+        <v>0.166</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1101,34 +1101,34 @@
         <v>18</v>
       </c>
       <c r="B19">
-        <v>20.894</v>
+        <v>0.146</v>
       </c>
       <c r="C19">
-        <v>0.374</v>
+        <v>0</v>
       </c>
       <c r="D19">
-        <v>0.612</v>
+        <v>0.004</v>
       </c>
       <c r="E19">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>19.637</v>
+        <v>0.138</v>
       </c>
       <c r="G19">
-        <v>22.035</v>
+        <v>0.154</v>
       </c>
       <c r="H19">
-        <v>19.6</v>
+        <v>0.138</v>
       </c>
       <c r="I19">
-        <v>22.007</v>
+        <v>0.154</v>
       </c>
       <c r="J19">
-        <v>19.722</v>
+        <v>0.138</v>
       </c>
       <c r="K19">
-        <v>22.13</v>
+        <v>0.154</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1141,34 +1141,34 @@
         <v>19</v>
       </c>
       <c r="B20">
-        <v>20.094</v>
+        <v>0.143</v>
       </c>
       <c r="C20">
-        <v>0.34</v>
+        <v>0</v>
       </c>
       <c r="D20">
-        <v>0.583</v>
+        <v>0.004</v>
       </c>
       <c r="E20">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <v>18.938</v>
+        <v>0.135</v>
       </c>
       <c r="G20">
-        <v>21.222</v>
+        <v>0.151</v>
       </c>
       <c r="H20">
-        <v>18.854</v>
+        <v>0.134</v>
       </c>
       <c r="I20">
-        <v>21.224</v>
+        <v>0.151</v>
       </c>
       <c r="J20">
-        <v>18.95</v>
+        <v>0.135</v>
       </c>
       <c r="K20">
-        <v>21.32</v>
+        <v>0.152</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1181,34 +1181,34 @@
         <v>20</v>
       </c>
       <c r="B21">
-        <v>19.637</v>
+        <v>0.137</v>
       </c>
       <c r="C21">
-        <v>0.347</v>
+        <v>0</v>
       </c>
       <c r="D21">
-        <v>0.589</v>
+        <v>0.004</v>
       </c>
       <c r="E21">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>18.408</v>
+        <v>0.129</v>
       </c>
       <c r="G21">
-        <v>20.717</v>
+        <v>0.145</v>
       </c>
       <c r="H21">
-        <v>18.345</v>
+        <v>0.129</v>
       </c>
       <c r="I21">
-        <v>20.723</v>
+        <v>0.145</v>
       </c>
       <c r="J21">
-        <v>18.477</v>
+        <v>0.13</v>
       </c>
       <c r="K21">
-        <v>20.855</v>
+        <v>0.145</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -1221,34 +1221,34 @@
         <v>21</v>
       </c>
       <c r="B22">
-        <v>18.891</v>
+        <v>0.135</v>
       </c>
       <c r="C22">
-        <v>0.39</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>0.625</v>
+        <v>0.004</v>
       </c>
       <c r="E22">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <v>17.68</v>
+        <v>0.127</v>
       </c>
       <c r="G22">
-        <v>20.129</v>
+        <v>0.143</v>
       </c>
       <c r="H22">
-        <v>17.669</v>
+        <v>0.126</v>
       </c>
       <c r="I22">
-        <v>20.101</v>
+        <v>0.143</v>
       </c>
       <c r="J22">
-        <v>17.694</v>
+        <v>0.127</v>
       </c>
       <c r="K22">
-        <v>20.126</v>
+        <v>0.144</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -1261,34 +1261,34 @@
         <v>22</v>
       </c>
       <c r="B23">
-        <v>17.35</v>
+        <v>0.123</v>
       </c>
       <c r="C23">
-        <v>0.294</v>
+        <v>0</v>
       </c>
       <c r="D23">
-        <v>0.542</v>
+        <v>0.004</v>
       </c>
       <c r="E23">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <v>16.322</v>
+        <v>0.115</v>
       </c>
       <c r="G23">
-        <v>18.449</v>
+        <v>0.13</v>
       </c>
       <c r="H23">
-        <v>16.288</v>
+        <v>0.115</v>
       </c>
       <c r="I23">
-        <v>18.488</v>
+        <v>0.13</v>
       </c>
       <c r="J23">
-        <v>16.247</v>
+        <v>0.116</v>
       </c>
       <c r="K23">
-        <v>18.448</v>
+        <v>0.13</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
@@ -1301,34 +1301,34 @@
         <v>23</v>
       </c>
       <c r="B24">
-        <v>17.204</v>
+        <v>0.122</v>
       </c>
       <c r="C24">
-        <v>0.353</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>0.594</v>
+        <v>0.004</v>
       </c>
       <c r="E24">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>16.042</v>
+        <v>0.114</v>
       </c>
       <c r="G24">
-        <v>18.371</v>
+        <v>0.129</v>
       </c>
       <c r="H24">
-        <v>16.031</v>
+        <v>0.114</v>
       </c>
       <c r="I24">
-        <v>18.412</v>
+        <v>0.129</v>
       </c>
       <c r="J24">
-        <v>15.998</v>
+        <v>0.114</v>
       </c>
       <c r="K24">
-        <v>18.379</v>
+        <v>0.13</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
@@ -1341,34 +1341,34 @@
         <v>24</v>
       </c>
       <c r="B25">
-        <v>15.641</v>
+        <v>0.112</v>
       </c>
       <c r="C25">
-        <v>0.243</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>0.492</v>
+        <v>0.004</v>
       </c>
       <c r="E25">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>14.663</v>
+        <v>0.105</v>
       </c>
       <c r="G25">
-        <v>16.594</v>
+        <v>0.119</v>
       </c>
       <c r="H25">
-        <v>14.594</v>
+        <v>0.105</v>
       </c>
       <c r="I25">
-        <v>16.509</v>
+        <v>0.119</v>
       </c>
       <c r="J25">
-        <v>14.761</v>
+        <v>0.105</v>
       </c>
       <c r="K25">
-        <v>16.675</v>
+        <v>0.119</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="B26">
-        <v>260.026</v>
+        <v>1.668</v>
       </c>
       <c r="C26">
-        <v>6.343</v>
+        <v>0</v>
       </c>
       <c r="D26">
-        <v>2.519</v>
+        <v>0.014</v>
       </c>
       <c r="E26">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <v>255.164</v>
+        <v>1.642</v>
       </c>
       <c r="G26">
-        <v>265.037</v>
+        <v>1.697</v>
       </c>
       <c r="H26">
-        <v>255.503</v>
+        <v>1.641</v>
       </c>
       <c r="I26">
-        <v>265.092</v>
+        <v>1.698</v>
       </c>
       <c r="J26">
-        <v>255.034</v>
+        <v>1.64</v>
       </c>
       <c r="K26">
-        <v>264.624</v>
+        <v>1.697</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
@@ -1421,34 +1421,34 @@
         <v>2</v>
       </c>
       <c r="B27">
-        <v>167.696</v>
+        <v>1.189</v>
       </c>
       <c r="C27">
-        <v>3.572</v>
+        <v>0</v>
       </c>
       <c r="D27">
-        <v>1.89</v>
+        <v>0.013</v>
       </c>
       <c r="E27">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>163.993</v>
+        <v>1.162</v>
       </c>
       <c r="G27">
-        <v>171.401</v>
+        <v>1.212</v>
       </c>
       <c r="H27">
-        <v>163.97</v>
+        <v>1.161</v>
       </c>
       <c r="I27">
-        <v>171.371</v>
+        <v>1.21</v>
       </c>
       <c r="J27">
-        <v>164.022</v>
+        <v>1.166</v>
       </c>
       <c r="K27">
-        <v>171.423</v>
+        <v>1.214</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -1461,34 +1461,34 @@
         <v>3</v>
       </c>
       <c r="B28">
-        <v>110.948</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="C28">
-        <v>2.483</v>
+        <v>0</v>
       </c>
       <c r="D28">
-        <v>1.576</v>
+        <v>0.01</v>
       </c>
       <c r="E28">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <v>107.778</v>
+        <v>0.789</v>
       </c>
       <c r="G28">
-        <v>113.954</v>
+        <v>0.827</v>
       </c>
       <c r="H28">
-        <v>107.713</v>
+        <v>0.789</v>
       </c>
       <c r="I28">
-        <v>113.801</v>
+        <v>0.827</v>
       </c>
       <c r="J28">
-        <v>108.014</v>
+        <v>0.79</v>
       </c>
       <c r="K28">
-        <v>114.101</v>
+        <v>0.827</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1501,34 +1501,34 @@
         <v>4</v>
       </c>
       <c r="B29">
-        <v>78.482</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="C29">
-        <v>2.413</v>
+        <v>0</v>
       </c>
       <c r="D29">
-        <v>1.553</v>
+        <v>0.008</v>
       </c>
       <c r="E29">
-        <v>0.049</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <v>75.252</v>
+        <v>0.549</v>
       </c>
       <c r="G29">
-        <v>81.34099999999999</v>
+        <v>0.582</v>
       </c>
       <c r="H29">
-        <v>74.908</v>
+        <v>0.548</v>
       </c>
       <c r="I29">
-        <v>81.102</v>
+        <v>0.582</v>
       </c>
       <c r="J29">
-        <v>75.67700000000001</v>
+        <v>0.549</v>
       </c>
       <c r="K29">
-        <v>81.87</v>
+        <v>0.583</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -1541,34 +1541,34 @@
         <v>5</v>
       </c>
       <c r="B30">
-        <v>60.934</v>
+        <v>0.433</v>
       </c>
       <c r="C30">
-        <v>1.003</v>
+        <v>0</v>
       </c>
       <c r="D30">
-        <v>1.002</v>
+        <v>0.007</v>
       </c>
       <c r="E30">
-        <v>0.032</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <v>58.986</v>
+        <v>0.418</v>
       </c>
       <c r="G30">
-        <v>62.912</v>
+        <v>0.447</v>
       </c>
       <c r="H30">
-        <v>58.906</v>
+        <v>0.418</v>
       </c>
       <c r="I30">
-        <v>62.857</v>
+        <v>0.446</v>
       </c>
       <c r="J30">
-        <v>59.026</v>
+        <v>0.419</v>
       </c>
       <c r="K30">
-        <v>62.977</v>
+        <v>0.447</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1581,34 +1581,34 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <v>49.339</v>
+        <v>0.344</v>
       </c>
       <c r="C31">
-        <v>0.825</v>
+        <v>0</v>
       </c>
       <c r="D31">
-        <v>0.908</v>
+        <v>0.006</v>
       </c>
       <c r="E31">
-        <v>0.029</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <v>47.576</v>
+        <v>0.333</v>
       </c>
       <c r="G31">
-        <v>51.136</v>
+        <v>0.357</v>
       </c>
       <c r="H31">
-        <v>47.536</v>
+        <v>0.333</v>
       </c>
       <c r="I31">
-        <v>51.184</v>
+        <v>0.357</v>
       </c>
       <c r="J31">
-        <v>47.511</v>
+        <v>0.332</v>
       </c>
       <c r="K31">
-        <v>51.158</v>
+        <v>0.357</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -1621,34 +1621,34 @@
         <v>7</v>
       </c>
       <c r="B32">
-        <v>42.948</v>
+        <v>0.288</v>
       </c>
       <c r="C32">
-        <v>0.917</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>0.958</v>
+        <v>0.006</v>
       </c>
       <c r="E32">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>41.081</v>
+        <v>0.278</v>
       </c>
       <c r="G32">
-        <v>44.836</v>
+        <v>0.3</v>
       </c>
       <c r="H32">
-        <v>40.93</v>
+        <v>0.278</v>
       </c>
       <c r="I32">
-        <v>44.717</v>
+        <v>0.299</v>
       </c>
       <c r="J32">
-        <v>41.19</v>
+        <v>0.278</v>
       </c>
       <c r="K32">
-        <v>44.977</v>
+        <v>0.3</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
@@ -1661,34 +1661,34 @@
         <v>8</v>
       </c>
       <c r="B33">
-        <v>37.392</v>
+        <v>0.249</v>
       </c>
       <c r="C33">
-        <v>0.755</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>0.869</v>
+        <v>0.005</v>
       </c>
       <c r="E33">
-        <v>0.027</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>35.704</v>
+        <v>0.239</v>
       </c>
       <c r="G33">
-        <v>39.11</v>
+        <v>0.26</v>
       </c>
       <c r="H33">
-        <v>35.735</v>
+        <v>0.238</v>
       </c>
       <c r="I33">
-        <v>39.163</v>
+        <v>0.259</v>
       </c>
       <c r="J33">
-        <v>35.636</v>
+        <v>0.239</v>
       </c>
       <c r="K33">
-        <v>39.064</v>
+        <v>0.26</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -1701,34 +1701,34 @@
         <v>9</v>
       </c>
       <c r="B34">
-        <v>33.456</v>
+        <v>0.222</v>
       </c>
       <c r="C34">
-        <v>0.618</v>
+        <v>0</v>
       </c>
       <c r="D34">
-        <v>0.786</v>
+        <v>0.005</v>
       </c>
       <c r="E34">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <v>31.935</v>
+        <v>0.212</v>
       </c>
       <c r="G34">
-        <v>35.016</v>
+        <v>0.231</v>
       </c>
       <c r="H34">
-        <v>31.922</v>
+        <v>0.212</v>
       </c>
       <c r="I34">
-        <v>34.982</v>
+        <v>0.232</v>
       </c>
       <c r="J34">
-        <v>31.949</v>
+        <v>0.212</v>
       </c>
       <c r="K34">
-        <v>35.009</v>
+        <v>0.232</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -1741,34 +1741,34 @@
         <v>10</v>
       </c>
       <c r="B35">
-        <v>32.202</v>
+        <v>0.212</v>
       </c>
       <c r="C35">
-        <v>0.627</v>
+        <v>0</v>
       </c>
       <c r="D35">
-        <v>0.792</v>
+        <v>0.005</v>
       </c>
       <c r="E35">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <v>30.611</v>
+        <v>0.202</v>
       </c>
       <c r="G35">
-        <v>33.715</v>
+        <v>0.221</v>
       </c>
       <c r="H35">
-        <v>30.515</v>
+        <v>0.202</v>
       </c>
       <c r="I35">
-        <v>33.68</v>
+        <v>0.221</v>
       </c>
       <c r="J35">
-        <v>30.685</v>
+        <v>0.202</v>
       </c>
       <c r="K35">
-        <v>33.85</v>
+        <v>0.221</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -1781,34 +1781,34 @@
         <v>11</v>
       </c>
       <c r="B36">
-        <v>30.067</v>
+        <v>0.197</v>
       </c>
       <c r="C36">
-        <v>0.702</v>
+        <v>0</v>
       </c>
       <c r="D36">
-        <v>0.838</v>
+        <v>0.005</v>
       </c>
       <c r="E36">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>28.509</v>
+        <v>0.187</v>
       </c>
       <c r="G36">
-        <v>31.793</v>
+        <v>0.207</v>
       </c>
       <c r="H36">
-        <v>28.347</v>
+        <v>0.187</v>
       </c>
       <c r="I36">
-        <v>31.697</v>
+        <v>0.207</v>
       </c>
       <c r="J36">
-        <v>28.522</v>
+        <v>0.187</v>
       </c>
       <c r="K36">
-        <v>31.872</v>
+        <v>0.207</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -1821,34 +1821,34 @@
         <v>12</v>
       </c>
       <c r="B37">
-        <v>31.085</v>
+        <v>0.202</v>
       </c>
       <c r="C37">
-        <v>0.668</v>
+        <v>0</v>
       </c>
       <c r="D37">
-        <v>0.8179999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="E37">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <v>29.449</v>
+        <v>0.193</v>
       </c>
       <c r="G37">
-        <v>32.653</v>
+        <v>0.211</v>
       </c>
       <c r="H37">
-        <v>29.398</v>
+        <v>0.193</v>
       </c>
       <c r="I37">
-        <v>32.657</v>
+        <v>0.211</v>
       </c>
       <c r="J37">
-        <v>29.479</v>
+        <v>0.193</v>
       </c>
       <c r="K37">
-        <v>32.738</v>
+        <v>0.211</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -1861,34 +1861,34 @@
         <v>13</v>
       </c>
       <c r="B38">
-        <v>26.265</v>
+        <v>0.172</v>
       </c>
       <c r="C38">
-        <v>0.482</v>
+        <v>0</v>
       </c>
       <c r="D38">
-        <v>0.694</v>
+        <v>0.004</v>
       </c>
       <c r="E38">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <v>24.894</v>
+        <v>0.164</v>
       </c>
       <c r="G38">
-        <v>27.614</v>
+        <v>0.18</v>
       </c>
       <c r="H38">
-        <v>24.815</v>
+        <v>0.164</v>
       </c>
       <c r="I38">
-        <v>27.514</v>
+        <v>0.18</v>
       </c>
       <c r="J38">
-        <v>25.006</v>
+        <v>0.164</v>
       </c>
       <c r="K38">
-        <v>27.704</v>
+        <v>0.18</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -1901,34 +1901,34 @@
         <v>14</v>
       </c>
       <c r="B39">
-        <v>26.879</v>
+        <v>0.171</v>
       </c>
       <c r="C39">
-        <v>0.513</v>
+        <v>0</v>
       </c>
       <c r="D39">
-        <v>0.716</v>
+        <v>0.004</v>
       </c>
       <c r="E39">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <v>25.489</v>
+        <v>0.163</v>
       </c>
       <c r="G39">
-        <v>28.296</v>
+        <v>0.179</v>
       </c>
       <c r="H39">
-        <v>25.386</v>
+        <v>0.162</v>
       </c>
       <c r="I39">
-        <v>28.22</v>
+        <v>0.179</v>
       </c>
       <c r="J39">
-        <v>25.552</v>
+        <v>0.162</v>
       </c>
       <c r="K39">
-        <v>28.385</v>
+        <v>0.179</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -1941,34 +1941,34 @@
         <v>15</v>
       </c>
       <c r="B40">
-        <v>25.065</v>
+        <v>0.162</v>
       </c>
       <c r="C40">
-        <v>0.521</v>
+        <v>0</v>
       </c>
       <c r="D40">
-        <v>0.722</v>
+        <v>0.004</v>
       </c>
       <c r="E40">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>23.636</v>
+        <v>0.154</v>
       </c>
       <c r="G40">
-        <v>26.465</v>
+        <v>0.17</v>
       </c>
       <c r="H40">
-        <v>23.58</v>
+        <v>0.154</v>
       </c>
       <c r="I40">
-        <v>26.493</v>
+        <v>0.17</v>
       </c>
       <c r="J40">
-        <v>23.622</v>
+        <v>0.154</v>
       </c>
       <c r="K40">
-        <v>26.535</v>
+        <v>0.17</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -1981,34 +1981,34 @@
         <v>16</v>
       </c>
       <c r="B41">
-        <v>24.628</v>
+        <v>0.162</v>
       </c>
       <c r="C41">
-        <v>0.49</v>
+        <v>0</v>
       </c>
       <c r="D41">
-        <v>0.7</v>
+        <v>0.004</v>
       </c>
       <c r="E41">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <v>23.268</v>
+        <v>0.153</v>
       </c>
       <c r="G41">
-        <v>26.013</v>
+        <v>0.17</v>
       </c>
       <c r="H41">
-        <v>23.297</v>
+        <v>0.153</v>
       </c>
       <c r="I41">
-        <v>25.926</v>
+        <v>0.17</v>
       </c>
       <c r="J41">
-        <v>23.343</v>
+        <v>0.154</v>
       </c>
       <c r="K41">
-        <v>25.972</v>
+        <v>0.171</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2021,34 +2021,34 @@
         <v>17</v>
       </c>
       <c r="B42">
-        <v>24.642</v>
+        <v>0.158</v>
       </c>
       <c r="C42">
-        <v>0.473</v>
+        <v>0</v>
       </c>
       <c r="D42">
-        <v>0.6879999999999999</v>
+        <v>0.004</v>
       </c>
       <c r="E42">
-        <v>0.022</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <v>23.311</v>
+        <v>0.15</v>
       </c>
       <c r="G42">
-        <v>26.007</v>
+        <v>0.166</v>
       </c>
       <c r="H42">
-        <v>23.328</v>
+        <v>0.15</v>
       </c>
       <c r="I42">
-        <v>25.986</v>
+        <v>0.166</v>
       </c>
       <c r="J42">
-        <v>23.315</v>
+        <v>0.15</v>
       </c>
       <c r="K42">
-        <v>25.973</v>
+        <v>0.166</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -2061,34 +2061,34 @@
         <v>18</v>
       </c>
       <c r="B43">
-        <v>22.336</v>
+        <v>0.146</v>
       </c>
       <c r="C43">
-        <v>0.441</v>
+        <v>0</v>
       </c>
       <c r="D43">
-        <v>0.664</v>
+        <v>0.004</v>
       </c>
       <c r="E43">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>21.053</v>
+        <v>0.138</v>
       </c>
       <c r="G43">
-        <v>23.656</v>
+        <v>0.153</v>
       </c>
       <c r="H43">
-        <v>20.946</v>
+        <v>0.137</v>
       </c>
       <c r="I43">
-        <v>23.632</v>
+        <v>0.153</v>
       </c>
       <c r="J43">
-        <v>21.058</v>
+        <v>0.138</v>
       </c>
       <c r="K43">
-        <v>23.744</v>
+        <v>0.153</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -2101,34 +2101,34 @@
         <v>19</v>
       </c>
       <c r="B44">
-        <v>22.268</v>
+        <v>0.142</v>
       </c>
       <c r="C44">
-        <v>1.307</v>
+        <v>0</v>
       </c>
       <c r="D44">
-        <v>1.143</v>
+        <v>0.004</v>
       </c>
       <c r="E44">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <v>20.046</v>
+        <v>0.134</v>
       </c>
       <c r="G44">
-        <v>24.527</v>
+        <v>0.15</v>
       </c>
       <c r="H44">
-        <v>19.653</v>
+        <v>0.134</v>
       </c>
       <c r="I44">
-        <v>24.134</v>
+        <v>0.15</v>
       </c>
       <c r="J44">
-        <v>20.42</v>
+        <v>0.134</v>
       </c>
       <c r="K44">
-        <v>24.901</v>
+        <v>0.15</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -2141,34 +2141,34 @@
         <v>20</v>
       </c>
       <c r="B45">
-        <v>21.095</v>
+        <v>0.137</v>
       </c>
       <c r="C45">
-        <v>0.41</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>0.64</v>
+        <v>0.004</v>
       </c>
       <c r="E45">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>19.832</v>
+        <v>0.129</v>
       </c>
       <c r="G45">
-        <v>22.342</v>
+        <v>0.144</v>
       </c>
       <c r="H45">
-        <v>19.837</v>
+        <v>0.129</v>
       </c>
       <c r="I45">
-        <v>22.327</v>
+        <v>0.144</v>
       </c>
       <c r="J45">
-        <v>19.855</v>
+        <v>0.129</v>
       </c>
       <c r="K45">
-        <v>22.345</v>
+        <v>0.144</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -2181,34 +2181,34 @@
         <v>21</v>
       </c>
       <c r="B46">
-        <v>20.388</v>
+        <v>0.135</v>
       </c>
       <c r="C46">
-        <v>0.421</v>
+        <v>0</v>
       </c>
       <c r="D46">
-        <v>0.649</v>
+        <v>0.004</v>
       </c>
       <c r="E46">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <v>19.1</v>
+        <v>0.127</v>
       </c>
       <c r="G46">
-        <v>21.642</v>
+        <v>0.143</v>
       </c>
       <c r="H46">
-        <v>19.073</v>
+        <v>0.127</v>
       </c>
       <c r="I46">
-        <v>21.624</v>
+        <v>0.143</v>
       </c>
       <c r="J46">
-        <v>19.134</v>
+        <v>0.128</v>
       </c>
       <c r="K46">
-        <v>21.686</v>
+        <v>0.144</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -2221,34 +2221,34 @@
         <v>22</v>
       </c>
       <c r="B47">
-        <v>18.511</v>
+        <v>0.121</v>
       </c>
       <c r="C47">
-        <v>0.33</v>
+        <v>0</v>
       </c>
       <c r="D47">
-        <v>0.574</v>
+        <v>0.004</v>
       </c>
       <c r="E47">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>17.358</v>
+        <v>0.114</v>
       </c>
       <c r="G47">
-        <v>19.61</v>
+        <v>0.128</v>
       </c>
       <c r="H47">
-        <v>17.35</v>
+        <v>0.114</v>
       </c>
       <c r="I47">
-        <v>19.626</v>
+        <v>0.128</v>
       </c>
       <c r="J47">
-        <v>17.369</v>
+        <v>0.114</v>
       </c>
       <c r="K47">
-        <v>19.644</v>
+        <v>0.128</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2261,34 +2261,34 @@
         <v>23</v>
       </c>
       <c r="B48">
-        <v>18.213</v>
+        <v>0.121</v>
       </c>
       <c r="C48">
-        <v>0.393</v>
+        <v>0</v>
       </c>
       <c r="D48">
-        <v>0.627</v>
+        <v>0.004</v>
       </c>
       <c r="E48">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <v>16.989</v>
+        <v>0.113</v>
       </c>
       <c r="G48">
-        <v>19.447</v>
+        <v>0.128</v>
       </c>
       <c r="H48">
-        <v>17.001</v>
+        <v>0.112</v>
       </c>
       <c r="I48">
-        <v>19.41</v>
+        <v>0.128</v>
       </c>
       <c r="J48">
-        <v>17.021</v>
+        <v>0.114</v>
       </c>
       <c r="K48">
-        <v>19.429</v>
+        <v>0.129</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -2301,34 +2301,34 @@
         <v>24</v>
       </c>
       <c r="B49">
-        <v>16.526</v>
+        <v>0.111</v>
       </c>
       <c r="C49">
-        <v>0.283</v>
+        <v>0</v>
       </c>
       <c r="D49">
-        <v>0.532</v>
+        <v>0.003</v>
       </c>
       <c r="E49">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <v>15.473</v>
+        <v>0.104</v>
       </c>
       <c r="G49">
-        <v>17.558</v>
+        <v>0.118</v>
       </c>
       <c r="H49">
-        <v>15.438</v>
+        <v>0.103</v>
       </c>
       <c r="I49">
-        <v>17.533</v>
+        <v>0.118</v>
       </c>
       <c r="J49">
-        <v>15.509</v>
+        <v>0.104</v>
       </c>
       <c r="K49">
-        <v>17.604</v>
+        <v>0.119</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
